--- a/outputs_xlsx_solution/test_new2.4-wide-NR-4.xlsx
+++ b/outputs_xlsx_solution/test_new2.4-wide-NR-4.xlsx
@@ -77,6 +77,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>WB</t>
   </si>
   <si>
@@ -123,6 +126,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -567,7 +573,7 @@
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -587,13 +593,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -613,13 +619,16 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
       </c>
       <c r="H4" t="s">
         <v>13</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -639,13 +648,22 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" t="s">
+        <v>14</v>
       </c>
       <c r="J5" t="s">
         <v>13</v>
       </c>
       <c r="K5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -665,16 +683,16 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
         <v>13</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -694,16 +712,16 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" t="s">
         <v>17</v>
       </c>
-      <c r="H7" t="s">
-        <v>16</v>
-      </c>
       <c r="K7" t="s">
         <v>13</v>
       </c>
       <c r="L7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -723,16 +741,16 @@
         <v>9</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L8" t="s">
         <v>13</v>
       </c>
       <c r="M8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -755,7 +773,7 @@
         <v>13</v>
       </c>
       <c r="P9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -775,13 +793,13 @@
         <v>9</v>
       </c>
       <c r="O10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P10" t="s">
         <v>13</v>
       </c>
       <c r="Q10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -801,13 +819,13 @@
         <v>9</v>
       </c>
       <c r="O11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="s">
         <v>13</v>
       </c>
       <c r="R11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -827,13 +845,13 @@
         <v>9</v>
       </c>
       <c r="P12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q12" t="s">
         <v>13</v>
       </c>
       <c r="R12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -853,13 +871,16 @@
         <v>9</v>
       </c>
       <c r="P13" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>14</v>
       </c>
       <c r="R13" t="s">
         <v>13</v>
       </c>
       <c r="S13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -879,16 +900,16 @@
         <v>9</v>
       </c>
       <c r="P14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S14" t="s">
         <v>13</v>
       </c>
       <c r="T14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -908,16 +929,16 @@
         <v>9</v>
       </c>
       <c r="Q15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S15" t="s">
         <v>13</v>
       </c>
       <c r="T15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -937,13 +958,16 @@
         <v>9</v>
       </c>
       <c r="R16" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="S16" t="s">
+        <v>14</v>
       </c>
       <c r="T16" t="s">
         <v>13</v>
       </c>
       <c r="U16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -963,21 +987,21 @@
         <v>9</v>
       </c>
       <c r="R17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U17" t="s">
         <v>13</v>
       </c>
       <c r="V17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -985,7 +1009,7 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -993,15 +1017,15 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -1009,39 +1033,55 @@
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
         <v>28</v>
       </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
         <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
